--- a/Res_ConvLSTM/DroughtDataset_model_testing_1753879301_h_3.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1753879301_h_3.xlsx
@@ -658,7 +658,7 @@
         <v>0.008417747105701008</v>
       </c>
       <c r="C2" t="n">
-        <v>18938934</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>18938934</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>14395984</v>
+        <v>4606479</v>
       </c>
       <c r="L2" t="n">
-        <v>8985747</v>
+        <v>2750502</v>
       </c>
       <c r="M2" t="n">
-        <v>2369836</v>
+        <v>695879</v>
       </c>
       <c r="N2" t="n">
-        <v>144546</v>
+        <v>36773</v>
       </c>
       <c r="O2" t="n">
-        <v>1386209</v>
+        <v>418949</v>
       </c>
       <c r="P2" t="n">
-        <v>540254</v>
+        <v>168428</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.999998152256012</v>
+        <v>0.9999982714653015</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9587780833244324</v>
+        <v>0.9200897216796875</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8944413065910339</v>
+        <v>0.8215905427932739</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8799217343330383</v>
+        <v>0.7755782008171082</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7609966993331909</v>
+        <v>0.5815016031265259</v>
       </c>
       <c r="V2" t="n">
-        <v>0.9070315361022949</v>
+        <v>0.8224749565124512</v>
       </c>
       <c r="W2" t="n">
-        <v>0.9359569549560547</v>
+        <v>0.8752825856208801</v>
       </c>
       <c r="X2" t="n">
-        <v>18938934</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>18938934</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>14462079</v>
+        <v>4815402</v>
       </c>
       <c r="AG2" t="n">
-        <v>8899088</v>
+        <v>2970254</v>
       </c>
       <c r="AH2" t="n">
-        <v>2397713</v>
+        <v>799435</v>
       </c>
       <c r="AI2" t="n">
-        <v>176916</v>
+        <v>58995</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1376789</v>
+        <v>459097</v>
       </c>
       <c r="AK2" t="n">
-        <v>540046</v>
+        <v>180028</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9566799402236938</v>
+        <v>0.9565494656562805</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9112439155578613</v>
+        <v>0.9113017320632935</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8581776022911072</v>
+        <v>0.8579359650611877</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6626315712928772</v>
+        <v>0.6623888611793518</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020464420318604</v>
+        <v>0.9020065665245056</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314221143722534</v>
+        <v>0.9314266443252563</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002018670822238358</v>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>14395984</v>
+        <v>4606479</v>
       </c>
       <c r="E3" t="n">
-        <v>697550</v>
+        <v>416553</v>
       </c>
       <c r="F3" t="n">
-        <v>6589</v>
+        <v>4613</v>
       </c>
       <c r="G3" t="n">
-        <v>1340</v>
+        <v>858</v>
       </c>
       <c r="H3" t="n">
-        <v>245</v>
+        <v>179</v>
       </c>
       <c r="I3" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J3" t="n">
-        <v>30049831</v>
+        <v>10016611</v>
       </c>
       <c r="K3" t="n">
-        <v>33268118</v>
+        <v>10900823</v>
       </c>
       <c r="L3" t="n">
-        <v>38149473</v>
+        <v>12468133</v>
       </c>
       <c r="M3" t="n">
-        <v>45870115</v>
+        <v>15196120</v>
       </c>
       <c r="N3" t="n">
-        <v>48676205</v>
+        <v>16214006</v>
       </c>
       <c r="O3" t="n">
-        <v>47319781</v>
+        <v>15729995</v>
       </c>
       <c r="P3" t="n">
-        <v>48371987</v>
+        <v>16112300</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9532666802406311</v>
+        <v>0.916037380695343</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9188949465751648</v>
+        <v>0.8426287174224854</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8477973341941833</v>
+        <v>0.7465551495552063</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5409696102142334</v>
+        <v>0.4125817716121674</v>
       </c>
       <c r="V3" t="n">
-        <v>0.9078369736671448</v>
+        <v>0.8227947950363159</v>
       </c>
       <c r="W3" t="n">
-        <v>0.9317197799682617</v>
+        <v>0.8713250160217285</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>14462079</v>
+        <v>4815402</v>
       </c>
       <c r="Z3" t="n">
-        <v>593526</v>
+        <v>197896</v>
       </c>
       <c r="AA3" t="n">
-        <v>25572</v>
+        <v>8540</v>
       </c>
       <c r="AB3" t="n">
-        <v>20336</v>
+        <v>6789</v>
       </c>
       <c r="AC3" t="n">
-        <v>135</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>30049866</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>33232195</v>
+        <v>11082162</v>
       </c>
       <c r="AG3" t="n">
-        <v>38343158</v>
+        <v>12776309</v>
       </c>
       <c r="AH3" t="n">
-        <v>45797268</v>
+        <v>15265103</v>
       </c>
       <c r="AI3" t="n">
-        <v>48631528</v>
+        <v>16210402</v>
       </c>
       <c r="AJ3" t="n">
-        <v>47312358</v>
+        <v>15770546</v>
       </c>
       <c r="AK3" t="n">
-        <v>48369192</v>
+        <v>16123045</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9576433300971985</v>
+        <v>0.957583487033844</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.910033106803894</v>
+        <v>0.9099507331848145</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8577702045440674</v>
+        <v>0.8576524257659912</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.662115752696991</v>
+        <v>0.6619057655334473</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9016677737236023</v>
+        <v>0.9016434550285339</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9313610792160034</v>
+        <v>0.9313350915908813</v>
       </c>
     </row>
     <row r="4">
@@ -929,127 +929,127 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>581860</v>
+        <v>378377</v>
       </c>
       <c r="E4" t="n">
-        <v>8985747</v>
+        <v>2750502</v>
       </c>
       <c r="F4" t="n">
-        <v>199794</v>
+        <v>126145</v>
       </c>
       <c r="G4" t="n">
-        <v>3849</v>
+        <v>2752</v>
       </c>
       <c r="H4" t="n">
-        <v>7216</v>
+        <v>6064</v>
       </c>
       <c r="I4" t="n">
-        <v>396</v>
+        <v>352</v>
       </c>
       <c r="J4" t="n">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="K4" t="n">
-        <v>618944</v>
+        <v>400075</v>
       </c>
       <c r="L4" t="n">
-        <v>1060465</v>
+        <v>597275</v>
       </c>
       <c r="M4" t="n">
-        <v>323399</v>
+        <v>201360</v>
       </c>
       <c r="N4" t="n">
-        <v>45397</v>
+        <v>26465</v>
       </c>
       <c r="O4" t="n">
-        <v>142083</v>
+        <v>90427</v>
       </c>
       <c r="P4" t="n">
-        <v>36967</v>
+        <v>23999</v>
       </c>
       <c r="Q4" t="n">
         <v>0.9999991059303284</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9560143947601318</v>
+        <v>0.9180591106414795</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9065032601356506</v>
+        <v>0.8319766521453857</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8635608553886414</v>
+        <v>0.7607899904251099</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6323912739753723</v>
+        <v>0.4826897978782654</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9074340462684631</v>
+        <v>0.8226348757743835</v>
       </c>
       <c r="W4" t="n">
-        <v>0.9338335990905762</v>
+        <v>0.8732993602752686</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>611398</v>
+        <v>204218</v>
       </c>
       <c r="Z4" t="n">
-        <v>8899088</v>
+        <v>2970254</v>
       </c>
       <c r="AA4" t="n">
-        <v>248302</v>
+        <v>83015</v>
       </c>
       <c r="AB4" t="n">
-        <v>16438</v>
+        <v>5489</v>
       </c>
       <c r="AC4" t="n">
-        <v>3432</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>204</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>654867</v>
+        <v>218736</v>
       </c>
       <c r="AG4" t="n">
-        <v>866780</v>
+        <v>289099</v>
       </c>
       <c r="AH4" t="n">
-        <v>396246</v>
+        <v>132377</v>
       </c>
       <c r="AI4" t="n">
-        <v>90074</v>
+        <v>30069</v>
       </c>
       <c r="AJ4" t="n">
-        <v>149506</v>
+        <v>49876</v>
       </c>
       <c r="AK4" t="n">
-        <v>39762</v>
+        <v>13254</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9571613669395447</v>
+        <v>0.9570662379264832</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106380939483643</v>
+        <v>0.910625696182251</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8579738140106201</v>
+        <v>0.8577942252159119</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6623735427856445</v>
+        <v>0.6621472835540771</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9018570184707642</v>
+        <v>0.9018250107765198</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313915967941284</v>
+        <v>0.9313808679580688</v>
       </c>
     </row>
     <row r="5">
@@ -1059,152 +1059,152 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>20817</v>
+        <v>12302</v>
       </c>
       <c r="E5" t="n">
-        <v>299569</v>
+        <v>157552</v>
       </c>
       <c r="F5" t="n">
-        <v>2369836</v>
+        <v>695879</v>
       </c>
       <c r="G5" t="n">
-        <v>21109</v>
+        <v>12135</v>
       </c>
       <c r="H5" t="n">
-        <v>80980</v>
+        <v>51855</v>
       </c>
       <c r="I5" t="n">
-        <v>2975</v>
+        <v>2397</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>705754</v>
+        <v>422223</v>
       </c>
       <c r="L5" t="n">
-        <v>793115</v>
+        <v>513690</v>
       </c>
       <c r="M5" t="n">
-        <v>425450</v>
+        <v>236241</v>
       </c>
       <c r="N5" t="n">
-        <v>122652</v>
+        <v>52356</v>
       </c>
       <c r="O5" t="n">
-        <v>140727</v>
+        <v>90229</v>
       </c>
       <c r="P5" t="n">
-        <v>39592</v>
+        <v>24873</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999992847442627</v>
+        <v>0.9999993443489075</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9729591608047485</v>
+        <v>0.9496437311172485</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9621632099151611</v>
+        <v>0.9319661855697632</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9847138524055481</v>
+        <v>0.9732019901275635</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9965696334838867</v>
+        <v>0.9951730966567993</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9942270517349243</v>
+        <v>0.9889369010925293</v>
       </c>
       <c r="W5" t="n">
-        <v>0.998437225818634</v>
+        <v>0.9970071315765381</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>23984</v>
+        <v>8010</v>
       </c>
       <c r="Z5" t="n">
-        <v>254565</v>
+        <v>84966</v>
       </c>
       <c r="AA5" t="n">
-        <v>2397713</v>
+        <v>799435</v>
       </c>
       <c r="AB5" t="n">
-        <v>29795</v>
+        <v>9941</v>
       </c>
       <c r="AC5" t="n">
-        <v>87330</v>
+        <v>29135</v>
       </c>
       <c r="AD5" t="n">
-        <v>1899</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>639659</v>
+        <v>213300</v>
       </c>
       <c r="AG5" t="n">
-        <v>879774</v>
+        <v>293938</v>
       </c>
       <c r="AH5" t="n">
-        <v>397573</v>
+        <v>132685</v>
       </c>
       <c r="AI5" t="n">
-        <v>90282</v>
+        <v>30134</v>
       </c>
       <c r="AJ5" t="n">
-        <v>150147</v>
+        <v>50081</v>
       </c>
       <c r="AK5" t="n">
-        <v>39800</v>
+        <v>13273</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9735750555992126</v>
+        <v>0.9735427498817444</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9643478989601135</v>
+        <v>0.9642956852912903</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837958812713623</v>
+        <v>0.9837679862976074</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963183999061584</v>
+        <v>0.9963132739067078</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938832521438599</v>
+        <v>0.9938787817955017</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983758926391602</v>
+        <v>0.9983755350112915</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>16152</v>
+        <v>9340</v>
       </c>
       <c r="E6" t="n">
-        <v>56971</v>
+        <v>17696</v>
       </c>
       <c r="F6" t="n">
-        <v>31585</v>
+        <v>15099</v>
       </c>
       <c r="G6" t="n">
-        <v>144546</v>
+        <v>36773</v>
       </c>
       <c r="H6" t="n">
-        <v>16777</v>
+        <v>9441</v>
       </c>
       <c r="I6" t="n">
-        <v>1148</v>
+        <v>774</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>19318</v>
+        <v>6452</v>
       </c>
       <c r="Z6" t="n">
-        <v>16016</v>
+        <v>5347</v>
       </c>
       <c r="AA6" t="n">
-        <v>32584</v>
+        <v>10875</v>
       </c>
       <c r="AB6" t="n">
-        <v>176916</v>
+        <v>58995</v>
       </c>
       <c r="AC6" t="n">
-        <v>20921</v>
+        <v>6979</v>
       </c>
       <c r="AD6" t="n">
-        <v>1443</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1263,22 +1263,22 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="E7" t="n">
-        <v>6021</v>
+        <v>5220</v>
       </c>
       <c r="F7" t="n">
-        <v>83892</v>
+        <v>54292</v>
       </c>
       <c r="G7" t="n">
-        <v>18339</v>
+        <v>10232</v>
       </c>
       <c r="H7" t="n">
-        <v>1386209</v>
+        <v>418949</v>
       </c>
       <c r="I7" t="n">
-        <v>32424</v>
+        <v>20459</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>83</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>2430</v>
+        <v>809</v>
       </c>
       <c r="AA7" t="n">
-        <v>88798</v>
+        <v>29617</v>
       </c>
       <c r="AB7" t="n">
-        <v>22710</v>
+        <v>7585</v>
       </c>
       <c r="AC7" t="n">
-        <v>1376789</v>
+        <v>459097</v>
       </c>
       <c r="AD7" t="n">
-        <v>36126</v>
+        <v>12042</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="E8" t="n">
-        <v>354</v>
+        <v>254</v>
       </c>
       <c r="F8" t="n">
-        <v>1539</v>
+        <v>1211</v>
       </c>
       <c r="G8" t="n">
-        <v>760</v>
+        <v>488</v>
       </c>
       <c r="H8" t="n">
-        <v>36865</v>
+        <v>22888</v>
       </c>
       <c r="I8" t="n">
-        <v>540254</v>
+        <v>168428</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>84</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>243</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>990</v>
+        <v>330</v>
       </c>
       <c r="AB8" t="n">
-        <v>795</v>
+        <v>265</v>
       </c>
       <c r="AC8" t="n">
-        <v>37688</v>
+        <v>12569</v>
       </c>
       <c r="AD8" t="n">
-        <v>540046</v>
+        <v>180028</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
